--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4108" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4108" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:33:27+00:00</t>
+    <t>2023-11-17T15:40:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -3442,10 +3445,10 @@
         <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3495,7 +3498,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3530,10 +3533,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3556,16 +3559,16 @@
         <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3615,7 +3618,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3650,10 +3653,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3676,16 +3679,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3711,13 +3714,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3735,7 +3738,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3756,10 +3759,10 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>80</v>
@@ -3770,10 +3773,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3796,16 +3799,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3831,13 +3834,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3855,7 +3858,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3876,10 +3879,10 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -3890,10 +3893,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3919,13 +3922,13 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3975,7 +3978,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -4010,10 +4013,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4036,16 +4039,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4071,13 +4074,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4095,7 +4098,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4130,14 +4133,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4156,16 +4159,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4215,7 +4218,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4239,7 +4242,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4250,14 +4253,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4276,16 +4279,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4335,7 +4338,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4370,10 +4373,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4402,7 +4405,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>117</v>
@@ -4455,7 +4458,7 @@
         <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4490,13 +4493,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
@@ -4518,13 +4521,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4575,7 +4578,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4610,13 +4613,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
@@ -4638,13 +4641,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4695,7 +4698,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4730,10 +4733,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4759,16 +4762,16 @@
         <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4817,7 +4820,7 @@
         <v>120</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4852,10 +4855,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4878,17 +4881,17 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4937,7 +4940,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4952,19 +4955,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4972,14 +4975,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4998,19 +5001,19 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5059,7 +5062,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5071,19 +5074,19 @@
         <v>103</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -5094,14 +5097,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5120,16 +5123,16 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5179,7 +5182,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5191,19 +5194,19 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -5214,10 +5217,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5240,19 +5243,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5277,13 +5280,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -5301,7 +5304,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -5316,19 +5319,19 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5336,10 +5339,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5362,19 +5365,19 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5399,19 +5402,19 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5421,7 +5424,7 @@
         <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5442,13 +5445,13 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5456,13 +5459,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>80</v>
@@ -5484,19 +5487,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5521,13 +5524,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -5545,7 +5548,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5566,13 +5569,13 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5580,10 +5583,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5698,10 +5701,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5818,10 +5821,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5844,19 +5847,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5905,7 +5908,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5926,10 +5929,10 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -5940,10 +5943,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6058,10 +6061,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6178,10 +6181,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6207,23 +6210,23 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>80</v>
@@ -6265,7 +6268,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6286,10 +6289,10 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6300,10 +6303,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6329,13 +6332,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6385,7 +6388,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6406,10 +6409,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6420,10 +6423,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6446,26 +6449,26 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>80</v>
@@ -6507,7 +6510,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6528,10 +6531,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6542,10 +6545,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6571,16 +6574,16 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6629,7 +6632,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6650,10 +6653,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6664,10 +6667,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6690,19 +6693,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6751,7 +6754,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6772,10 +6775,10 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6786,10 +6789,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6815,16 +6818,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6873,7 +6876,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6894,10 +6897,10 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6908,14 +6911,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6934,19 +6937,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6971,13 +6974,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6995,7 +6998,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -7010,30 +7013,30 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7148,10 +7151,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7268,10 +7271,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7294,19 +7297,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7316,7 +7319,7 @@
         <v>80</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>80</v>
@@ -7355,7 +7358,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7376,10 +7379,10 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -7390,10 +7393,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7419,16 +7422,16 @@
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7477,7 +7480,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7498,10 +7501,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7512,10 +7515,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7538,19 +7541,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7599,7 +7602,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7611,22 +7614,22 @@
         <v>103</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7634,10 +7637,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7660,16 +7663,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7719,7 +7722,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7731,7 +7734,7 @@
         <v>103</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7740,13 +7743,13 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7754,14 +7757,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7780,19 +7783,19 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7841,7 +7844,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7853,22 +7856,22 @@
         <v>103</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7876,14 +7879,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7902,19 +7905,19 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7963,7 +7966,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7972,25 +7975,25 @@
         <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7998,10 +8001,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8027,13 +8030,13 @@
         <v>129</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8083,7 +8086,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8104,13 +8107,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8118,10 +8121,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8144,19 +8147,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -8205,7 +8208,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8217,22 +8220,22 @@
         <v>103</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>80</v>
@@ -8240,10 +8243,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8266,19 +8269,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8288,7 +8291,7 @@
         <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>80</v>
@@ -8327,7 +8330,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8336,7 +8339,7 @@
         <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -8345,27 +8348,27 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8480,10 +8483,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8600,10 +8603,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8626,19 +8629,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8687,7 +8690,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8708,10 +8711,10 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8722,10 +8725,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8748,25 +8751,25 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="R53" t="s" s="2">
         <v>80</v>
@@ -8787,13 +8790,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8811,7 +8814,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8832,10 +8835,10 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8846,10 +8849,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8875,16 +8878,16 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8894,7 +8897,7 @@
         <v>80</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>80</v>
@@ -8933,7 +8936,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8954,10 +8957,10 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8968,10 +8971,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8997,16 +9000,16 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -9055,7 +9058,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9064,7 +9067,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -9076,10 +9079,10 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -9090,10 +9093,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9116,19 +9119,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -9177,7 +9180,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9198,10 +9201,10 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -9212,10 +9215,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9238,19 +9241,19 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9275,13 +9278,13 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -9299,7 +9302,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9308,7 +9311,7 @@
         <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>104</v>
@@ -9323,7 +9326,7 @@
         <v>105</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -9334,10 +9337,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9452,10 +9455,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9572,10 +9575,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9598,19 +9601,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9659,7 +9662,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9680,10 +9683,10 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9694,10 +9697,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9812,10 +9815,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9932,10 +9935,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9961,16 +9964,16 @@
         <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -10019,7 +10022,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10040,10 +10043,10 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10054,10 +10057,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10083,13 +10086,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10139,7 +10142,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10160,10 +10163,10 @@
         <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10174,10 +10177,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10200,19 +10203,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10261,7 +10264,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10282,10 +10285,10 @@
         <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -10296,10 +10299,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10325,16 +10328,16 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10383,7 +10386,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10404,10 +10407,10 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10418,10 +10421,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10444,19 +10447,19 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10505,7 +10508,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10526,10 +10529,10 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -10540,10 +10543,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10569,16 +10572,16 @@
         <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10627,7 +10630,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10648,10 +10651,10 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10662,14 +10665,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10688,19 +10691,19 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10725,13 +10728,13 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10749,7 +10752,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10767,27 +10770,27 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10810,19 +10813,19 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10871,7 +10874,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10892,10 +10895,10 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10906,10 +10909,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10932,16 +10935,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10967,13 +10970,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10991,7 +10994,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -11009,27 +11012,27 @@
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11052,19 +11055,19 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -11089,13 +11092,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -11113,7 +11116,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -11134,10 +11137,10 @@
         <v>80</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -11148,10 +11151,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11266,10 +11269,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11386,10 +11389,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11412,19 +11415,19 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11473,7 +11476,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11494,10 +11497,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11508,10 +11511,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11626,10 +11629,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11746,10 +11749,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11775,16 +11778,16 @@
         <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11833,7 +11836,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11854,10 +11857,10 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11868,10 +11871,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11897,13 +11900,13 @@
         <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11953,7 +11956,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11974,10 +11977,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11988,10 +11991,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12014,19 +12017,19 @@
         <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12075,7 +12078,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12096,10 +12099,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12110,10 +12113,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12139,16 +12142,16 @@
         <v>107</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -12197,7 +12200,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12218,10 +12221,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12232,10 +12235,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12258,19 +12261,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -12319,7 +12322,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12340,10 +12343,10 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12354,10 +12357,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12383,16 +12386,16 @@
         <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12441,7 +12444,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12462,10 +12465,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12476,10 +12479,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12502,16 +12505,16 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12561,7 +12564,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12573,33 +12576,33 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12622,16 +12625,16 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12681,7 +12684,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12693,33 +12696,33 @@
         <v>103</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12742,19 +12745,19 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12803,7 +12806,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12815,7 +12818,7 @@
         <v>103</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>80</v>
@@ -12824,10 +12827,10 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12838,10 +12841,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12956,10 +12959,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13076,14 +13079,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13105,16 +13108,16 @@
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -13163,7 +13166,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13198,10 +13201,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13224,16 +13227,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13283,7 +13286,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13292,10 +13295,10 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
@@ -13304,10 +13307,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13318,10 +13321,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13344,16 +13347,16 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13403,7 +13406,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13412,10 +13415,10 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
@@ -13424,10 +13427,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13438,10 +13441,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13464,19 +13467,19 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13501,13 +13504,13 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -13525,7 +13528,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13543,13 +13546,13 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13560,10 +13563,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13586,19 +13589,19 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13623,13 +13626,13 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13647,7 +13650,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13665,13 +13668,13 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13682,10 +13685,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13708,19 +13711,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13769,7 +13772,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13781,7 +13784,7 @@
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
@@ -13790,10 +13793,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13804,10 +13807,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13833,13 +13836,13 @@
         <v>107</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13889,7 +13892,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13910,10 +13913,10 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13924,10 +13927,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13950,16 +13953,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14009,7 +14012,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14021,7 +14024,7 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>80</v>
@@ -14030,10 +14033,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14044,10 +14047,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14070,16 +14073,16 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14129,7 +14132,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14141,7 +14144,7 @@
         <v>103</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>80</v>
@@ -14150,10 +14153,10 @@
         <v>80</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>80</v>
@@ -14164,10 +14167,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14190,19 +14193,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -14251,7 +14254,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14263,7 +14266,7 @@
         <v>103</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
@@ -14272,10 +14275,10 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14286,10 +14289,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14404,10 +14407,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14524,14 +14527,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14553,16 +14556,16 @@
         <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14611,7 +14614,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14646,10 +14649,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14672,19 +14675,19 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14709,13 +14712,13 @@
         <v>80</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>80</v>
@@ -14733,7 +14736,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>91</v>
@@ -14751,16 +14754,16 @@
         <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>80</v>
@@ -14768,10 +14771,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14794,19 +14797,19 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14831,13 +14834,13 @@
         <v>80</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>80</v>
@@ -14855,7 +14858,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14864,7 +14867,7 @@
         <v>91</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>104</v>
@@ -14873,27 +14876,27 @@
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14916,19 +14919,19 @@
         <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14953,13 +14956,13 @@
         <v>80</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>80</v>
@@ -14977,7 +14980,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14986,7 +14989,7 @@
         <v>91</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>104</v>
@@ -15001,7 +15004,7 @@
         <v>105</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -15012,14 +15015,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15038,19 +15041,19 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -15075,13 +15078,13 @@
         <v>80</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>80</v>
@@ -15099,7 +15102,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15117,27 +15120,27 @@
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15163,16 +15166,16 @@
         <v>81</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -15221,7 +15224,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15242,10 +15245,10 @@
         <v>80</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>

--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:40:40+00:00</t>
+    <t>2023-11-23T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
